--- a/Elevator_All_Models_DB_FULLDATA_v03.xlsx
+++ b/Elevator_All_Models_DB_FULLDATA_v03.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1104"/>
+  <dimension ref="A1:G1126"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -36864,6 +36864,732 @@
         <v>3</v>
       </c>
     </row>
+    <row r="1105">
+      <c r="A1105" t="inlineStr">
+        <is>
+          <t>NexWay-S</t>
+        </is>
+      </c>
+      <c r="B1105" t="inlineStr">
+        <is>
+          <t>China [MESE]</t>
+        </is>
+      </c>
+      <c r="C1105" t="inlineStr">
+        <is>
+          <t>MELCO</t>
+        </is>
+      </c>
+      <c r="D1105" t="inlineStr">
+        <is>
+          <t>Passenger elevator</t>
+        </is>
+      </c>
+      <c r="E1105" t="inlineStr">
+        <is>
+          <t>Machine room</t>
+        </is>
+      </c>
+      <c r="F1105" t="n">
+        <v>2000</v>
+      </c>
+      <c r="G1105" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1106">
+      <c r="A1106" t="inlineStr">
+        <is>
+          <t>NexWay-S</t>
+        </is>
+      </c>
+      <c r="B1106" t="inlineStr">
+        <is>
+          <t>China [MESE]</t>
+        </is>
+      </c>
+      <c r="C1106" t="inlineStr">
+        <is>
+          <t>MELCO</t>
+        </is>
+      </c>
+      <c r="D1106" t="inlineStr">
+        <is>
+          <t>Passenger elevator</t>
+        </is>
+      </c>
+      <c r="E1106" t="inlineStr">
+        <is>
+          <t>Machine room</t>
+        </is>
+      </c>
+      <c r="F1106" t="n">
+        <v>2000</v>
+      </c>
+      <c r="G1106" t="n">
+        <v>1.6</v>
+      </c>
+    </row>
+    <row r="1107">
+      <c r="A1107" t="inlineStr">
+        <is>
+          <t>NexWay-S</t>
+        </is>
+      </c>
+      <c r="B1107" t="inlineStr">
+        <is>
+          <t>China [MESE]</t>
+        </is>
+      </c>
+      <c r="C1107" t="inlineStr">
+        <is>
+          <t>MELCO</t>
+        </is>
+      </c>
+      <c r="D1107" t="inlineStr">
+        <is>
+          <t>Passenger elevator</t>
+        </is>
+      </c>
+      <c r="E1107" t="inlineStr">
+        <is>
+          <t>Machine room</t>
+        </is>
+      </c>
+      <c r="F1107" t="n">
+        <v>2000</v>
+      </c>
+      <c r="G1107" t="n">
+        <v>1.75</v>
+      </c>
+    </row>
+    <row r="1108">
+      <c r="A1108" t="inlineStr">
+        <is>
+          <t>NexWay-S</t>
+        </is>
+      </c>
+      <c r="B1108" t="inlineStr">
+        <is>
+          <t>China [MESE]</t>
+        </is>
+      </c>
+      <c r="C1108" t="inlineStr">
+        <is>
+          <t>MELCO</t>
+        </is>
+      </c>
+      <c r="D1108" t="inlineStr">
+        <is>
+          <t>Passenger elevator</t>
+        </is>
+      </c>
+      <c r="E1108" t="inlineStr">
+        <is>
+          <t>Machine room</t>
+        </is>
+      </c>
+      <c r="F1108" t="n">
+        <v>2000</v>
+      </c>
+      <c r="G1108" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1109">
+      <c r="A1109" t="inlineStr">
+        <is>
+          <t>NexWay-S</t>
+        </is>
+      </c>
+      <c r="B1109" t="inlineStr">
+        <is>
+          <t>China [MESE]</t>
+        </is>
+      </c>
+      <c r="C1109" t="inlineStr">
+        <is>
+          <t>MELCO</t>
+        </is>
+      </c>
+      <c r="D1109" t="inlineStr">
+        <is>
+          <t>Passenger elevator</t>
+        </is>
+      </c>
+      <c r="E1109" t="inlineStr">
+        <is>
+          <t>Machine room</t>
+        </is>
+      </c>
+      <c r="F1109" t="n">
+        <v>2250</v>
+      </c>
+      <c r="G1109" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1110">
+      <c r="A1110" t="inlineStr">
+        <is>
+          <t>NexWay-S</t>
+        </is>
+      </c>
+      <c r="B1110" t="inlineStr">
+        <is>
+          <t>China [MESE]</t>
+        </is>
+      </c>
+      <c r="C1110" t="inlineStr">
+        <is>
+          <t>MELCO</t>
+        </is>
+      </c>
+      <c r="D1110" t="inlineStr">
+        <is>
+          <t>Passenger elevator</t>
+        </is>
+      </c>
+      <c r="E1110" t="inlineStr">
+        <is>
+          <t>Machine room</t>
+        </is>
+      </c>
+      <c r="F1110" t="n">
+        <v>2250</v>
+      </c>
+      <c r="G1110" t="n">
+        <v>1.6</v>
+      </c>
+    </row>
+    <row r="1111">
+      <c r="A1111" t="inlineStr">
+        <is>
+          <t>NexWay-S</t>
+        </is>
+      </c>
+      <c r="B1111" t="inlineStr">
+        <is>
+          <t>China [MESE]</t>
+        </is>
+      </c>
+      <c r="C1111" t="inlineStr">
+        <is>
+          <t>MELCO</t>
+        </is>
+      </c>
+      <c r="D1111" t="inlineStr">
+        <is>
+          <t>Passenger elevator</t>
+        </is>
+      </c>
+      <c r="E1111" t="inlineStr">
+        <is>
+          <t>Machine room</t>
+        </is>
+      </c>
+      <c r="F1111" t="n">
+        <v>2250</v>
+      </c>
+      <c r="G1111" t="n">
+        <v>1.75</v>
+      </c>
+    </row>
+    <row r="1112">
+      <c r="A1112" t="inlineStr">
+        <is>
+          <t>NexWay-S</t>
+        </is>
+      </c>
+      <c r="B1112" t="inlineStr">
+        <is>
+          <t>China [MESE]</t>
+        </is>
+      </c>
+      <c r="C1112" t="inlineStr">
+        <is>
+          <t>MELCO</t>
+        </is>
+      </c>
+      <c r="D1112" t="inlineStr">
+        <is>
+          <t>Passenger elevator</t>
+        </is>
+      </c>
+      <c r="E1112" t="inlineStr">
+        <is>
+          <t>Machine room</t>
+        </is>
+      </c>
+      <c r="F1112" t="n">
+        <v>2250</v>
+      </c>
+      <c r="G1112" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1113">
+      <c r="A1113" t="inlineStr">
+        <is>
+          <t>NexWay-S</t>
+        </is>
+      </c>
+      <c r="B1113" t="inlineStr">
+        <is>
+          <t>China [MESE]</t>
+        </is>
+      </c>
+      <c r="C1113" t="inlineStr">
+        <is>
+          <t>MELCO</t>
+        </is>
+      </c>
+      <c r="D1113" t="inlineStr">
+        <is>
+          <t>Passenger elevator</t>
+        </is>
+      </c>
+      <c r="E1113" t="inlineStr">
+        <is>
+          <t>Machine room</t>
+        </is>
+      </c>
+      <c r="F1113" t="n">
+        <v>2500</v>
+      </c>
+      <c r="G1113" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1114">
+      <c r="A1114" t="inlineStr">
+        <is>
+          <t>NexWay-S</t>
+        </is>
+      </c>
+      <c r="B1114" t="inlineStr">
+        <is>
+          <t>China [MESE]</t>
+        </is>
+      </c>
+      <c r="C1114" t="inlineStr">
+        <is>
+          <t>MELCO</t>
+        </is>
+      </c>
+      <c r="D1114" t="inlineStr">
+        <is>
+          <t>Passenger elevator</t>
+        </is>
+      </c>
+      <c r="E1114" t="inlineStr">
+        <is>
+          <t>Machine room</t>
+        </is>
+      </c>
+      <c r="F1114" t="n">
+        <v>2500</v>
+      </c>
+      <c r="G1114" t="n">
+        <v>1.6</v>
+      </c>
+    </row>
+    <row r="1115">
+      <c r="A1115" t="inlineStr">
+        <is>
+          <t>NexWay-S</t>
+        </is>
+      </c>
+      <c r="B1115" t="inlineStr">
+        <is>
+          <t>China [MESE]</t>
+        </is>
+      </c>
+      <c r="C1115" t="inlineStr">
+        <is>
+          <t>MELCO</t>
+        </is>
+      </c>
+      <c r="D1115" t="inlineStr">
+        <is>
+          <t>Passenger elevator</t>
+        </is>
+      </c>
+      <c r="E1115" t="inlineStr">
+        <is>
+          <t>Machine room</t>
+        </is>
+      </c>
+      <c r="F1115" t="n">
+        <v>2500</v>
+      </c>
+      <c r="G1115" t="n">
+        <v>1.75</v>
+      </c>
+    </row>
+    <row r="1116">
+      <c r="A1116" t="inlineStr">
+        <is>
+          <t>NexWay-S</t>
+        </is>
+      </c>
+      <c r="B1116" t="inlineStr">
+        <is>
+          <t>China [MESE]</t>
+        </is>
+      </c>
+      <c r="C1116" t="inlineStr">
+        <is>
+          <t>EN81-20/50</t>
+        </is>
+      </c>
+      <c r="D1116" t="inlineStr">
+        <is>
+          <t>Passenger elevator</t>
+        </is>
+      </c>
+      <c r="E1116" t="inlineStr">
+        <is>
+          <t>Machine room</t>
+        </is>
+      </c>
+      <c r="F1116" t="n">
+        <v>2000</v>
+      </c>
+      <c r="G1116" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1117">
+      <c r="A1117" t="inlineStr">
+        <is>
+          <t>NexWay-S</t>
+        </is>
+      </c>
+      <c r="B1117" t="inlineStr">
+        <is>
+          <t>China [MESE]</t>
+        </is>
+      </c>
+      <c r="C1117" t="inlineStr">
+        <is>
+          <t>EN81-20/50</t>
+        </is>
+      </c>
+      <c r="D1117" t="inlineStr">
+        <is>
+          <t>Passenger elevator</t>
+        </is>
+      </c>
+      <c r="E1117" t="inlineStr">
+        <is>
+          <t>Machine room</t>
+        </is>
+      </c>
+      <c r="F1117" t="n">
+        <v>2000</v>
+      </c>
+      <c r="G1117" t="n">
+        <v>1.6</v>
+      </c>
+    </row>
+    <row r="1118">
+      <c r="A1118" t="inlineStr">
+        <is>
+          <t>NexWay-S</t>
+        </is>
+      </c>
+      <c r="B1118" t="inlineStr">
+        <is>
+          <t>China [MESE]</t>
+        </is>
+      </c>
+      <c r="C1118" t="inlineStr">
+        <is>
+          <t>EN81-20/50</t>
+        </is>
+      </c>
+      <c r="D1118" t="inlineStr">
+        <is>
+          <t>Passenger elevator</t>
+        </is>
+      </c>
+      <c r="E1118" t="inlineStr">
+        <is>
+          <t>Machine room</t>
+        </is>
+      </c>
+      <c r="F1118" t="n">
+        <v>2000</v>
+      </c>
+      <c r="G1118" t="n">
+        <v>1.75</v>
+      </c>
+    </row>
+    <row r="1119">
+      <c r="A1119" t="inlineStr">
+        <is>
+          <t>NexWay-S</t>
+        </is>
+      </c>
+      <c r="B1119" t="inlineStr">
+        <is>
+          <t>China [MESE]</t>
+        </is>
+      </c>
+      <c r="C1119" t="inlineStr">
+        <is>
+          <t>EN81-20/50</t>
+        </is>
+      </c>
+      <c r="D1119" t="inlineStr">
+        <is>
+          <t>Passenger elevator</t>
+        </is>
+      </c>
+      <c r="E1119" t="inlineStr">
+        <is>
+          <t>Machine room</t>
+        </is>
+      </c>
+      <c r="F1119" t="n">
+        <v>2000</v>
+      </c>
+      <c r="G1119" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1120">
+      <c r="A1120" t="inlineStr">
+        <is>
+          <t>NexWay-S</t>
+        </is>
+      </c>
+      <c r="B1120" t="inlineStr">
+        <is>
+          <t>China [MESE]</t>
+        </is>
+      </c>
+      <c r="C1120" t="inlineStr">
+        <is>
+          <t>EN81-20/50</t>
+        </is>
+      </c>
+      <c r="D1120" t="inlineStr">
+        <is>
+          <t>Passenger elevator</t>
+        </is>
+      </c>
+      <c r="E1120" t="inlineStr">
+        <is>
+          <t>Machine room</t>
+        </is>
+      </c>
+      <c r="F1120" t="n">
+        <v>2250</v>
+      </c>
+      <c r="G1120" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1121">
+      <c r="A1121" t="inlineStr">
+        <is>
+          <t>NexWay-S</t>
+        </is>
+      </c>
+      <c r="B1121" t="inlineStr">
+        <is>
+          <t>China [MESE]</t>
+        </is>
+      </c>
+      <c r="C1121" t="inlineStr">
+        <is>
+          <t>EN81-20/50</t>
+        </is>
+      </c>
+      <c r="D1121" t="inlineStr">
+        <is>
+          <t>Passenger elevator</t>
+        </is>
+      </c>
+      <c r="E1121" t="inlineStr">
+        <is>
+          <t>Machine room</t>
+        </is>
+      </c>
+      <c r="F1121" t="n">
+        <v>2250</v>
+      </c>
+      <c r="G1121" t="n">
+        <v>1.6</v>
+      </c>
+    </row>
+    <row r="1122">
+      <c r="A1122" t="inlineStr">
+        <is>
+          <t>NexWay-S</t>
+        </is>
+      </c>
+      <c r="B1122" t="inlineStr">
+        <is>
+          <t>China [MESE]</t>
+        </is>
+      </c>
+      <c r="C1122" t="inlineStr">
+        <is>
+          <t>EN81-20/50</t>
+        </is>
+      </c>
+      <c r="D1122" t="inlineStr">
+        <is>
+          <t>Passenger elevator</t>
+        </is>
+      </c>
+      <c r="E1122" t="inlineStr">
+        <is>
+          <t>Machine room</t>
+        </is>
+      </c>
+      <c r="F1122" t="n">
+        <v>2250</v>
+      </c>
+      <c r="G1122" t="n">
+        <v>1.75</v>
+      </c>
+    </row>
+    <row r="1123">
+      <c r="A1123" t="inlineStr">
+        <is>
+          <t>NexWay-S</t>
+        </is>
+      </c>
+      <c r="B1123" t="inlineStr">
+        <is>
+          <t>China [MESE]</t>
+        </is>
+      </c>
+      <c r="C1123" t="inlineStr">
+        <is>
+          <t>EN81-20/50</t>
+        </is>
+      </c>
+      <c r="D1123" t="inlineStr">
+        <is>
+          <t>Passenger elevator</t>
+        </is>
+      </c>
+      <c r="E1123" t="inlineStr">
+        <is>
+          <t>Machine room</t>
+        </is>
+      </c>
+      <c r="F1123" t="n">
+        <v>2250</v>
+      </c>
+      <c r="G1123" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1124">
+      <c r="A1124" t="inlineStr">
+        <is>
+          <t>NexWay-S</t>
+        </is>
+      </c>
+      <c r="B1124" t="inlineStr">
+        <is>
+          <t>China [MESE]</t>
+        </is>
+      </c>
+      <c r="C1124" t="inlineStr">
+        <is>
+          <t>EN81-20/50</t>
+        </is>
+      </c>
+      <c r="D1124" t="inlineStr">
+        <is>
+          <t>Passenger elevator</t>
+        </is>
+      </c>
+      <c r="E1124" t="inlineStr">
+        <is>
+          <t>Machine room</t>
+        </is>
+      </c>
+      <c r="F1124" t="n">
+        <v>2500</v>
+      </c>
+      <c r="G1124" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1125">
+      <c r="A1125" t="inlineStr">
+        <is>
+          <t>NexWay-S</t>
+        </is>
+      </c>
+      <c r="B1125" t="inlineStr">
+        <is>
+          <t>China [MESE]</t>
+        </is>
+      </c>
+      <c r="C1125" t="inlineStr">
+        <is>
+          <t>EN81-20/50</t>
+        </is>
+      </c>
+      <c r="D1125" t="inlineStr">
+        <is>
+          <t>Passenger elevator</t>
+        </is>
+      </c>
+      <c r="E1125" t="inlineStr">
+        <is>
+          <t>Machine room</t>
+        </is>
+      </c>
+      <c r="F1125" t="n">
+        <v>2500</v>
+      </c>
+      <c r="G1125" t="n">
+        <v>1.6</v>
+      </c>
+    </row>
+    <row r="1126">
+      <c r="A1126" t="inlineStr">
+        <is>
+          <t>NexWay-S</t>
+        </is>
+      </c>
+      <c r="B1126" t="inlineStr">
+        <is>
+          <t>China [MESE]</t>
+        </is>
+      </c>
+      <c r="C1126" t="inlineStr">
+        <is>
+          <t>EN81-20/50</t>
+        </is>
+      </c>
+      <c r="D1126" t="inlineStr">
+        <is>
+          <t>Passenger elevator</t>
+        </is>
+      </c>
+      <c r="E1126" t="inlineStr">
+        <is>
+          <t>Machine room</t>
+        </is>
+      </c>
+      <c r="F1126" t="n">
+        <v>2500</v>
+      </c>
+      <c r="G1126" t="n">
+        <v>1.75</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
